--- a/Nhom_DAP01.xlsx
+++ b/Nhom_DAP01.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iannwendy/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iannwendy/Desktop/SOA-139_523H0054_CuoiKyV1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D809A2F4-D0DA-544E-9377-007AA3190D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81E3E645-0166-444B-8E7F-8903898117E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" xr2:uid="{26352C60-855D-E843-A083-A5990A866B49}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="83">
   <si>
     <t>Thành viên</t>
   </si>
@@ -279,6 +279,15 @@
   </si>
   <si>
     <t>DECORATOR PATTERN</t>
+  </si>
+  <si>
+    <t>Thực hiện P1-2-3</t>
+  </si>
+  <si>
+    <t>Thực hiện P7-8-9</t>
+  </si>
+  <si>
+    <t>Thực hiện P4-5-6</t>
   </si>
 </sst>
 </file>
@@ -937,7 +946,9 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>82</v>
+      </c>
       <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
@@ -957,7 +968,9 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="12" t="s">
+        <v>81</v>
+      </c>
       <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,9 +988,13 @@
       <c r="D5" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="11">
+        <v>335568825</v>
+      </c>
       <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="G5" s="11" t="s">
+        <v>80</v>
+      </c>
       <c r="H5" s="1" t="s">
         <v>8</v>
       </c>
